--- a/data/questions.xlsx
+++ b/data/questions.xlsx
@@ -397,49 +397,99 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:N2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>id</v>
       </c>
       <c r="B1" t="str">
+        <v>subject</v>
+      </c>
+      <c r="C1" t="str">
         <v>category</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
+        <v>subcategory</v>
+      </c>
+      <c r="E1" t="str">
         <v>difficulty</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>question</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>choice_a</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>choice_b</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>choice_c</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>choice_d</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>correct_answer</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>explanation</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>source</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>createdAt</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>question_59ebfc84-ef08-433c-9316-cd33339eb19b</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Government Law &amp; Ethics</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Government Law &amp; Ethics</v>
+      </c>
+      <c r="D2" t="str">
+        <v>พ.ร.บ.ระเบียบบริหารราชการแผ่นดิน 2534</v>
+      </c>
+      <c r="E2" t="str">
+        <v>medium</v>
+      </c>
+      <c r="F2" t="str">
+        <v>ข้อใดเกี่ยวข้องกับ พ.ร.บ.ระเบียบบริหารราชการแผ่นดิน 2534?</v>
+      </c>
+      <c r="G2" t="str">
+        <v>พ.ร.ฎ.วิธีการบริหารกิจการบ้านเมืองที่ดี 2546</v>
+      </c>
+      <c r="H2" t="str">
+        <v>พ.ร.บ.ความรับผิดและการละเมิดของเจ้าหน้าที่</v>
+      </c>
+      <c r="I2" t="str">
+        <v>ป.อ.2499 (ในส่วนความผิดต่อตำแหน่งหน้าที่ราชการ)</v>
+      </c>
+      <c r="J2" t="str">
+        <v>พ.ร.บ.ระเบียบบริหารราชการแผ่นดิน 2534</v>
+      </c>
+      <c r="K2" t="str">
+        <v>D</v>
+      </c>
+      <c r="L2" t="str">
+        <v>กฎหมายที่เกี่ยวข้องคือ พ.ร.บ.ระเบียบบริหารราชการแผ่นดิน 2534</v>
+      </c>
+      <c r="M2" t="str">
+        <v>llm</v>
+      </c>
+      <c r="N2" t="str">
+        <v>2026-03-15T16:28:08.352Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/questions.xlsx
+++ b/data/questions.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:O22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -442,6 +442,9 @@
       <c r="N1" t="str">
         <v>createdAt</v>
       </c>
+      <c r="O1" t="str">
+        <v>created_at</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -487,9 +490,949 @@
         <v>2026-03-15T16:28:08.352Z</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>9c97c8c5-7e99-4c28-90fd-a13b4081245d</v>
+      </c>
+      <c r="B3" t="str">
+        <v>math</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Analytical Thinking</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Percentage</v>
+      </c>
+      <c r="E3" t="str">
+        <v>medium</v>
+      </c>
+      <c r="F3" t="str">
+        <v>หาก 26 - x = 10, ค่า x เท่ากับเท่าใด?</v>
+      </c>
+      <c r="G3" t="str">
+        <v>-16</v>
+      </c>
+      <c r="H3" t="str">
+        <v>17</v>
+      </c>
+      <c r="I3" t="str">
+        <v>18</v>
+      </c>
+      <c r="J3" t="str">
+        <v>15</v>
+      </c>
+      <c r="K3" t="str">
+        <v>A</v>
+      </c>
+      <c r="L3" t="str">
+        <v>แก้สมการให้ได้ค่า x = -16</v>
+      </c>
+      <c r="M3" t="str">
+        <v>ai</v>
+      </c>
+      <c r="N3" t="str">
+        <v>2026-03-16T12:36:19.709Z</v>
+      </c>
+      <c r="O3" t="str">
+        <v>2026-03-16T12:36:19.709Z</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>19b0eb1a-e205-4df1-8f83-8e214c30e6ea</v>
+      </c>
+      <c r="B4" t="str">
+        <v>math</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Analytical Thinking</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Percentage</v>
+      </c>
+      <c r="E4" t="str">
+        <v>medium</v>
+      </c>
+      <c r="F4" t="str">
+        <v>หาก 5 - x = -12, ค่า x เท่ากับเท่าใด?</v>
+      </c>
+      <c r="G4" t="str">
+        <v>19</v>
+      </c>
+      <c r="H4" t="str">
+        <v>-17</v>
+      </c>
+      <c r="I4" t="str">
+        <v>16</v>
+      </c>
+      <c r="J4" t="str">
+        <v>18</v>
+      </c>
+      <c r="K4" t="str">
+        <v>B</v>
+      </c>
+      <c r="L4" t="str">
+        <v>แก้สมการให้ได้ค่า x = -17</v>
+      </c>
+      <c r="M4" t="str">
+        <v>ai</v>
+      </c>
+      <c r="N4" t="str">
+        <v>2026-03-16T12:36:19.710Z</v>
+      </c>
+      <c r="O4" t="str">
+        <v>2026-03-16T12:36:19.710Z</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>8486c4d3-9b0d-4bbd-8160-a2da5c2e67ac</v>
+      </c>
+      <c r="B5" t="str">
+        <v>math</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Analytical Thinking</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Percentage</v>
+      </c>
+      <c r="E5" t="str">
+        <v>medium</v>
+      </c>
+      <c r="F5" t="str">
+        <v>หาก 14 + x = 32, ค่า x เท่ากับเท่าใด?</v>
+      </c>
+      <c r="G5" t="str">
+        <v>18</v>
+      </c>
+      <c r="H5" t="str">
+        <v>17</v>
+      </c>
+      <c r="I5" t="str">
+        <v>19</v>
+      </c>
+      <c r="J5" t="str">
+        <v>20</v>
+      </c>
+      <c r="K5" t="str">
+        <v>A</v>
+      </c>
+      <c r="L5" t="str">
+        <v>แก้สมการให้ได้ค่า x = 18</v>
+      </c>
+      <c r="M5" t="str">
+        <v>ai</v>
+      </c>
+      <c r="N5" t="str">
+        <v>2026-03-16T12:36:19.710Z</v>
+      </c>
+      <c r="O5" t="str">
+        <v>2026-03-16T12:36:19.710Z</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3026d8ab-fbee-44c7-bc8f-80c2e6992ccc</v>
+      </c>
+      <c r="B6" t="str">
+        <v>math</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Analytical Thinking</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Percentage</v>
+      </c>
+      <c r="E6" t="str">
+        <v>medium</v>
+      </c>
+      <c r="F6" t="str">
+        <v>หาก 2 + x = 7, ค่า x เท่ากับเท่าใด?</v>
+      </c>
+      <c r="G6" t="str">
+        <v>4</v>
+      </c>
+      <c r="H6" t="str">
+        <v>5</v>
+      </c>
+      <c r="I6" t="str">
+        <v>6</v>
+      </c>
+      <c r="J6" t="str">
+        <v>7</v>
+      </c>
+      <c r="K6" t="str">
+        <v>B</v>
+      </c>
+      <c r="L6" t="str">
+        <v>แก้สมการให้ได้ค่า x = 5</v>
+      </c>
+      <c r="M6" t="str">
+        <v>ai</v>
+      </c>
+      <c r="N6" t="str">
+        <v>2026-03-16T12:36:19.710Z</v>
+      </c>
+      <c r="O6" t="str">
+        <v>2026-03-16T12:36:19.710Z</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>a239bfad-1410-445b-b67c-b65e709e83a8</v>
+      </c>
+      <c r="B7" t="str">
+        <v>math</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Analytical Thinking</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Percentage</v>
+      </c>
+      <c r="E7" t="str">
+        <v>medium</v>
+      </c>
+      <c r="F7" t="str">
+        <v>หาก 30 - x = 20, ค่า x เท่ากับเท่าใด?</v>
+      </c>
+      <c r="G7" t="str">
+        <v>9</v>
+      </c>
+      <c r="H7" t="str">
+        <v>-10</v>
+      </c>
+      <c r="I7" t="str">
+        <v>12</v>
+      </c>
+      <c r="J7" t="str">
+        <v>11</v>
+      </c>
+      <c r="K7" t="str">
+        <v>B</v>
+      </c>
+      <c r="L7" t="str">
+        <v>แก้สมการให้ได้ค่า x = -10</v>
+      </c>
+      <c r="M7" t="str">
+        <v>ai</v>
+      </c>
+      <c r="N7" t="str">
+        <v>2026-03-16T12:36:19.710Z</v>
+      </c>
+      <c r="O7" t="str">
+        <v>2026-03-16T12:36:19.710Z</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>6cf1d0cd-1450-4f84-b1c0-0ad0d75d4db4</v>
+      </c>
+      <c r="B8" t="str">
+        <v>math</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Analytical Thinking</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Percentage</v>
+      </c>
+      <c r="E8" t="str">
+        <v>medium</v>
+      </c>
+      <c r="F8" t="str">
+        <v>หาก 13 - x = -1, ค่า x เท่ากับเท่าใด?</v>
+      </c>
+      <c r="G8" t="str">
+        <v>13</v>
+      </c>
+      <c r="H8" t="str">
+        <v>-14</v>
+      </c>
+      <c r="I8" t="str">
+        <v>15</v>
+      </c>
+      <c r="J8" t="str">
+        <v>16</v>
+      </c>
+      <c r="K8" t="str">
+        <v>B</v>
+      </c>
+      <c r="L8" t="str">
+        <v>แก้สมการให้ได้ค่า x = -14</v>
+      </c>
+      <c r="M8" t="str">
+        <v>ai</v>
+      </c>
+      <c r="N8" t="str">
+        <v>2026-03-16T12:36:19.710Z</v>
+      </c>
+      <c r="O8" t="str">
+        <v>2026-03-16T12:36:19.710Z</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>da3535b7-5dc9-43bb-9843-f397ea6d07ce</v>
+      </c>
+      <c r="B9" t="str">
+        <v>math</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Analytical Thinking</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Percentage</v>
+      </c>
+      <c r="E9" t="str">
+        <v>medium</v>
+      </c>
+      <c r="F9" t="str">
+        <v>หาก 29 + x = 40, ค่า x เท่ากับเท่าใด?</v>
+      </c>
+      <c r="G9" t="str">
+        <v>13</v>
+      </c>
+      <c r="H9" t="str">
+        <v>10</v>
+      </c>
+      <c r="I9" t="str">
+        <v>11</v>
+      </c>
+      <c r="J9" t="str">
+        <v>12</v>
+      </c>
+      <c r="K9" t="str">
+        <v>C</v>
+      </c>
+      <c r="L9" t="str">
+        <v>แก้สมการให้ได้ค่า x = 11</v>
+      </c>
+      <c r="M9" t="str">
+        <v>ai</v>
+      </c>
+      <c r="N9" t="str">
+        <v>2026-03-16T12:36:19.710Z</v>
+      </c>
+      <c r="O9" t="str">
+        <v>2026-03-16T12:36:19.710Z</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>169f9a68-e43a-4dbb-91b1-62600b497699</v>
+      </c>
+      <c r="B10" t="str">
+        <v>math</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Analytical Thinking</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Percentage</v>
+      </c>
+      <c r="E10" t="str">
+        <v>medium</v>
+      </c>
+      <c r="F10" t="str">
+        <v>หาก 21 + x = 22, ค่า x เท่ากับเท่าใด?</v>
+      </c>
+      <c r="G10" t="str">
+        <v>1</v>
+      </c>
+      <c r="H10" t="str">
+        <v>3</v>
+      </c>
+      <c r="I10" t="str">
+        <v>1</v>
+      </c>
+      <c r="J10" t="str">
+        <v>2</v>
+      </c>
+      <c r="K10" t="str">
+        <v>A</v>
+      </c>
+      <c r="L10" t="str">
+        <v>แก้สมการให้ได้ค่า x = 1</v>
+      </c>
+      <c r="M10" t="str">
+        <v>ai</v>
+      </c>
+      <c r="N10" t="str">
+        <v>2026-03-16T12:36:19.710Z</v>
+      </c>
+      <c r="O10" t="str">
+        <v>2026-03-16T12:36:19.710Z</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>54330dc9-320d-4ea6-8e03-68d67129605d</v>
+      </c>
+      <c r="B11" t="str">
+        <v>math</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Analytical Thinking</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Percentage</v>
+      </c>
+      <c r="E11" t="str">
+        <v>medium</v>
+      </c>
+      <c r="F11" t="str">
+        <v>หาก 12 - x = -2, ค่า x เท่ากับเท่าใด?</v>
+      </c>
+      <c r="G11" t="str">
+        <v>13</v>
+      </c>
+      <c r="H11" t="str">
+        <v>-14</v>
+      </c>
+      <c r="I11" t="str">
+        <v>16</v>
+      </c>
+      <c r="J11" t="str">
+        <v>15</v>
+      </c>
+      <c r="K11" t="str">
+        <v>B</v>
+      </c>
+      <c r="L11" t="str">
+        <v>แก้สมการให้ได้ค่า x = -14</v>
+      </c>
+      <c r="M11" t="str">
+        <v>ai</v>
+      </c>
+      <c r="N11" t="str">
+        <v>2026-03-16T12:36:19.710Z</v>
+      </c>
+      <c r="O11" t="str">
+        <v>2026-03-16T12:36:19.710Z</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>6f194a14-86c0-485b-9ea1-4797d32a6b0a</v>
+      </c>
+      <c r="B12" t="str">
+        <v>math</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Analytical Thinking</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Percentage</v>
+      </c>
+      <c r="E12" t="str">
+        <v>medium</v>
+      </c>
+      <c r="F12" t="str">
+        <v>หาก 21 - x = 3, ค่า x เท่ากับเท่าใด?</v>
+      </c>
+      <c r="G12" t="str">
+        <v>17</v>
+      </c>
+      <c r="H12" t="str">
+        <v>19</v>
+      </c>
+      <c r="I12" t="str">
+        <v>20</v>
+      </c>
+      <c r="J12" t="str">
+        <v>-18</v>
+      </c>
+      <c r="K12" t="str">
+        <v>D</v>
+      </c>
+      <c r="L12" t="str">
+        <v>แก้สมการให้ได้ค่า x = -18</v>
+      </c>
+      <c r="M12" t="str">
+        <v>ai</v>
+      </c>
+      <c r="N12" t="str">
+        <v>2026-03-16T12:36:19.710Z</v>
+      </c>
+      <c r="O12" t="str">
+        <v>2026-03-16T12:36:19.710Z</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>89013e11-3860-4f98-8d53-a7d4598e010d</v>
+      </c>
+      <c r="B13" t="str">
+        <v>math</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Analytical Thinking</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Percentage</v>
+      </c>
+      <c r="E13" t="str">
+        <v>medium</v>
+      </c>
+      <c r="F13" t="str">
+        <v>หาก 27 + x = 28, ค่า x เท่ากับเท่าใด?</v>
+      </c>
+      <c r="G13" t="str">
+        <v>1</v>
+      </c>
+      <c r="H13" t="str">
+        <v>2</v>
+      </c>
+      <c r="I13" t="str">
+        <v>1</v>
+      </c>
+      <c r="J13" t="str">
+        <v>3</v>
+      </c>
+      <c r="K13" t="str">
+        <v>A</v>
+      </c>
+      <c r="L13" t="str">
+        <v>แก้สมการให้ได้ค่า x = 1</v>
+      </c>
+      <c r="M13" t="str">
+        <v>ai</v>
+      </c>
+      <c r="N13" t="str">
+        <v>2026-03-16T12:36:19.711Z</v>
+      </c>
+      <c r="O13" t="str">
+        <v>2026-03-16T12:36:19.711Z</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>a94c48aa-9e26-4e84-8f80-bb7231c24e70</v>
+      </c>
+      <c r="B14" t="str">
+        <v>math</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Analytical Thinking</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Percentage</v>
+      </c>
+      <c r="E14" t="str">
+        <v>medium</v>
+      </c>
+      <c r="F14" t="str">
+        <v>หาก 16 + x = 28, ค่า x เท่ากับเท่าใด?</v>
+      </c>
+      <c r="G14" t="str">
+        <v>12</v>
+      </c>
+      <c r="H14" t="str">
+        <v>11</v>
+      </c>
+      <c r="I14" t="str">
+        <v>14</v>
+      </c>
+      <c r="J14" t="str">
+        <v>13</v>
+      </c>
+      <c r="K14" t="str">
+        <v>A</v>
+      </c>
+      <c r="L14" t="str">
+        <v>แก้สมการให้ได้ค่า x = 12</v>
+      </c>
+      <c r="M14" t="str">
+        <v>ai</v>
+      </c>
+      <c r="N14" t="str">
+        <v>2026-03-16T12:36:19.711Z</v>
+      </c>
+      <c r="O14" t="str">
+        <v>2026-03-16T12:36:19.711Z</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>779c940e-2552-4069-a7b6-f8dbd48f8288</v>
+      </c>
+      <c r="B15" t="str">
+        <v>math</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Analytical Thinking</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Percentage</v>
+      </c>
+      <c r="E15" t="str">
+        <v>medium</v>
+      </c>
+      <c r="F15" t="str">
+        <v>หาก 30 - x = 26, ค่า x เท่ากับเท่าใด?</v>
+      </c>
+      <c r="G15" t="str">
+        <v>-4</v>
+      </c>
+      <c r="H15" t="str">
+        <v>3</v>
+      </c>
+      <c r="I15" t="str">
+        <v>6</v>
+      </c>
+      <c r="J15" t="str">
+        <v>5</v>
+      </c>
+      <c r="K15" t="str">
+        <v>A</v>
+      </c>
+      <c r="L15" t="str">
+        <v>แก้สมการให้ได้ค่า x = -4</v>
+      </c>
+      <c r="M15" t="str">
+        <v>ai</v>
+      </c>
+      <c r="N15" t="str">
+        <v>2026-03-16T12:36:19.711Z</v>
+      </c>
+      <c r="O15" t="str">
+        <v>2026-03-16T12:36:19.711Z</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>adea2f59-b01b-4a3c-8ca3-81213c72bdf8</v>
+      </c>
+      <c r="B16" t="str">
+        <v>math</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Analytical Thinking</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Percentage</v>
+      </c>
+      <c r="E16" t="str">
+        <v>medium</v>
+      </c>
+      <c r="F16" t="str">
+        <v>หาก 18 - x = -2, ค่า x เท่ากับเท่าใด?</v>
+      </c>
+      <c r="G16" t="str">
+        <v>21</v>
+      </c>
+      <c r="H16" t="str">
+        <v>22</v>
+      </c>
+      <c r="I16" t="str">
+        <v>19</v>
+      </c>
+      <c r="J16" t="str">
+        <v>-20</v>
+      </c>
+      <c r="K16" t="str">
+        <v>D</v>
+      </c>
+      <c r="L16" t="str">
+        <v>แก้สมการให้ได้ค่า x = -20</v>
+      </c>
+      <c r="M16" t="str">
+        <v>ai</v>
+      </c>
+      <c r="N16" t="str">
+        <v>2026-03-16T12:36:19.711Z</v>
+      </c>
+      <c r="O16" t="str">
+        <v>2026-03-16T12:36:19.711Z</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>f3bc0a9e-6e47-479a-a611-7a84066b36a5</v>
+      </c>
+      <c r="B17" t="str">
+        <v>math</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Analytical Thinking</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Percentage</v>
+      </c>
+      <c r="E17" t="str">
+        <v>medium</v>
+      </c>
+      <c r="F17" t="str">
+        <v>หาก 8 + x = 20, ค่า x เท่ากับเท่าใด?</v>
+      </c>
+      <c r="G17" t="str">
+        <v>11</v>
+      </c>
+      <c r="H17" t="str">
+        <v>14</v>
+      </c>
+      <c r="I17" t="str">
+        <v>13</v>
+      </c>
+      <c r="J17" t="str">
+        <v>12</v>
+      </c>
+      <c r="K17" t="str">
+        <v>D</v>
+      </c>
+      <c r="L17" t="str">
+        <v>แก้สมการให้ได้ค่า x = 12</v>
+      </c>
+      <c r="M17" t="str">
+        <v>ai</v>
+      </c>
+      <c r="N17" t="str">
+        <v>2026-03-16T12:36:19.711Z</v>
+      </c>
+      <c r="O17" t="str">
+        <v>2026-03-16T12:36:19.711Z</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>962ba188-a651-4f10-a47c-c348e1c222a0</v>
+      </c>
+      <c r="B18" t="str">
+        <v>math</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Analytical Thinking</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Percentage</v>
+      </c>
+      <c r="E18" t="str">
+        <v>medium</v>
+      </c>
+      <c r="F18" t="str">
+        <v>หาก 17 - x = 12, ค่า x เท่ากับเท่าใด?</v>
+      </c>
+      <c r="G18" t="str">
+        <v>-5</v>
+      </c>
+      <c r="H18" t="str">
+        <v>7</v>
+      </c>
+      <c r="I18" t="str">
+        <v>4</v>
+      </c>
+      <c r="J18" t="str">
+        <v>6</v>
+      </c>
+      <c r="K18" t="str">
+        <v>A</v>
+      </c>
+      <c r="L18" t="str">
+        <v>แก้สมการให้ได้ค่า x = -5</v>
+      </c>
+      <c r="M18" t="str">
+        <v>ai</v>
+      </c>
+      <c r="N18" t="str">
+        <v>2026-03-16T12:36:19.711Z</v>
+      </c>
+      <c r="O18" t="str">
+        <v>2026-03-16T12:36:19.711Z</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>30595f87-95a5-435f-8331-dd10d7245dcf</v>
+      </c>
+      <c r="B19" t="str">
+        <v>math</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Analytical Thinking</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Percentage</v>
+      </c>
+      <c r="E19" t="str">
+        <v>medium</v>
+      </c>
+      <c r="F19" t="str">
+        <v>หาก 27 - x = 17, ค่า x เท่ากับเท่าใด?</v>
+      </c>
+      <c r="G19" t="str">
+        <v>9</v>
+      </c>
+      <c r="H19" t="str">
+        <v>12</v>
+      </c>
+      <c r="I19" t="str">
+        <v>-10</v>
+      </c>
+      <c r="J19" t="str">
+        <v>11</v>
+      </c>
+      <c r="K19" t="str">
+        <v>C</v>
+      </c>
+      <c r="L19" t="str">
+        <v>แก้สมการให้ได้ค่า x = -10</v>
+      </c>
+      <c r="M19" t="str">
+        <v>ai</v>
+      </c>
+      <c r="N19" t="str">
+        <v>2026-03-16T12:36:19.711Z</v>
+      </c>
+      <c r="O19" t="str">
+        <v>2026-03-16T12:36:19.711Z</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>b63586e0-bbc4-4dba-bbfa-d52a73fb2be8</v>
+      </c>
+      <c r="B20" t="str">
+        <v>math</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Analytical Thinking</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Percentage</v>
+      </c>
+      <c r="E20" t="str">
+        <v>medium</v>
+      </c>
+      <c r="F20" t="str">
+        <v>หาก 27 - x = 7, ค่า x เท่ากับเท่าใด?</v>
+      </c>
+      <c r="G20" t="str">
+        <v>21</v>
+      </c>
+      <c r="H20" t="str">
+        <v>-20</v>
+      </c>
+      <c r="I20" t="str">
+        <v>19</v>
+      </c>
+      <c r="J20" t="str">
+        <v>22</v>
+      </c>
+      <c r="K20" t="str">
+        <v>B</v>
+      </c>
+      <c r="L20" t="str">
+        <v>แก้สมการให้ได้ค่า x = -20</v>
+      </c>
+      <c r="M20" t="str">
+        <v>ai</v>
+      </c>
+      <c r="N20" t="str">
+        <v>2026-03-16T12:36:19.711Z</v>
+      </c>
+      <c r="O20" t="str">
+        <v>2026-03-16T12:36:19.711Z</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>a9479ddf-038a-4d60-b4c4-09a07c00b006</v>
+      </c>
+      <c r="B21" t="str">
+        <v>math</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Analytical Thinking</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Percentage</v>
+      </c>
+      <c r="E21" t="str">
+        <v>medium</v>
+      </c>
+      <c r="F21" t="str">
+        <v>หาก 13 + x = 31, ค่า x เท่ากับเท่าใด?</v>
+      </c>
+      <c r="G21" t="str">
+        <v>17</v>
+      </c>
+      <c r="H21" t="str">
+        <v>20</v>
+      </c>
+      <c r="I21" t="str">
+        <v>18</v>
+      </c>
+      <c r="J21" t="str">
+        <v>19</v>
+      </c>
+      <c r="K21" t="str">
+        <v>C</v>
+      </c>
+      <c r="L21" t="str">
+        <v>แก้สมการให้ได้ค่า x = 18</v>
+      </c>
+      <c r="M21" t="str">
+        <v>ai</v>
+      </c>
+      <c r="N21" t="str">
+        <v>2026-03-16T12:36:19.711Z</v>
+      </c>
+      <c r="O21" t="str">
+        <v>2026-03-16T12:36:19.711Z</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>da688307-a92f-4538-b758-2e1103cb0d7d</v>
+      </c>
+      <c r="B22" t="str">
+        <v>math</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Analytical Thinking</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Percentage</v>
+      </c>
+      <c r="E22" t="str">
+        <v>medium</v>
+      </c>
+      <c r="F22" t="str">
+        <v>หาก 28 + x = 42, ค่า x เท่ากับเท่าใด?</v>
+      </c>
+      <c r="G22" t="str">
+        <v>14</v>
+      </c>
+      <c r="H22" t="str">
+        <v>13</v>
+      </c>
+      <c r="I22" t="str">
+        <v>15</v>
+      </c>
+      <c r="J22" t="str">
+        <v>16</v>
+      </c>
+      <c r="K22" t="str">
+        <v>A</v>
+      </c>
+      <c r="L22" t="str">
+        <v>แก้สมการให้ได้ค่า x = 14</v>
+      </c>
+      <c r="M22" t="str">
+        <v>ai</v>
+      </c>
+      <c r="N22" t="str">
+        <v>2026-03-16T12:36:19.711Z</v>
+      </c>
+      <c r="O22" t="str">
+        <v>2026-03-16T12:36:19.711Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O22"/>
   </ignoredErrors>
 </worksheet>
 </file>